--- a/StocksIC/tdxFSCode.xlsx
+++ b/StocksIC/tdxFSCode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12255"/>
+    <workbookView windowWidth="21600" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="df" sheetId="1" r:id="rId1"/>
@@ -1583,7 +1583,7 @@
     <t>col219</t>
   </si>
   <si>
-    <t>每股经营性现金流(元)</t>
+    <t>每股经营性现金流</t>
   </si>
   <si>
     <t>col220</t>
@@ -1619,7 +1619,7 @@
     <t>col225</t>
   </si>
   <si>
-    <t>每股现金流量净额(元)</t>
+    <t>每股现金流量净额</t>
   </si>
   <si>
     <t>col226</t>
@@ -1952,7 +1952,7 @@
     <t>col276</t>
   </si>
   <si>
-    <t>近一年净利润(元)</t>
+    <t>近一年净利润</t>
   </si>
   <si>
     <t>col277</t>
@@ -3370,7 +3370,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3390,9 +3390,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -13415,7 +13412,7 @@
       <c r="H327" t="s">
         <v>744</v>
       </c>
-      <c r="I327" s="7" t="s">
+      <c r="I327" s="2" t="s">
         <v>745</v>
       </c>
     </row>
@@ -13937,7 +13934,7 @@
       <c r="H345" t="s">
         <v>780</v>
       </c>
-      <c r="I345" s="7" t="s">
+      <c r="I345" s="2" t="s">
         <v>781</v>
       </c>
     </row>
@@ -14946,7 +14943,7 @@
       <c r="H380" t="s">
         <v>851</v>
       </c>
-      <c r="I380" s="8" t="s">
+      <c r="I380" s="7" t="s">
         <v>852</v>
       </c>
     </row>
@@ -15642,7 +15639,7 @@
       <c r="H404" t="s">
         <v>900</v>
       </c>
-      <c r="I404" s="9" t="s">
+      <c r="I404" s="8" t="s">
         <v>901</v>
       </c>
     </row>

--- a/StocksIC/tdxFSCode.xlsx
+++ b/StocksIC/tdxFSCode.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9675"/>
+    <workbookView windowWidth="20745" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="df" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3227" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="903">
   <si>
     <t>Index</t>
   </si>
@@ -1604,6 +1604,9 @@
     <t>销售商品提供劳务收到的现金/营业收入(%)</t>
   </si>
   <si>
+    <t>销售收现/营收</t>
+  </si>
+  <si>
     <t>col223</t>
   </si>
   <si>
@@ -1637,7 +1640,7 @@
     <t>col228</t>
   </si>
   <si>
-    <t>经营活动现金净流量与净利润比率</t>
+    <t>经营活动现金净流量/净利润</t>
   </si>
   <si>
     <t>col229</t>
@@ -2748,7 +2751,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2761,6 +2764,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3240,16 +3249,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3258,119 +3264,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3390,6 +3399,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -3931,7 +3943,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I404"/>
+  <dimension ref="A1:J404"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6.375" customWidth="1"/>
@@ -3943,6 +3955,7 @@
     <col min="7" max="7" width="35.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.625" customWidth="1"/>
     <col min="9" max="9" width="65.125" customWidth="1"/>
+    <col min="10" max="10" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -10371,7 +10384,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" ht="17.25" spans="1:10">
       <c r="A223">
         <v>221</v>
       </c>
@@ -10398,6 +10411,9 @@
       </c>
       <c r="I223" t="s">
         <v>523</v>
+      </c>
+      <c r="J223" s="6" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -10423,10 +10439,10 @@
         <v>515</v>
       </c>
       <c r="H224" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I224" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -10452,10 +10468,10 @@
         <v>515</v>
       </c>
       <c r="H225" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I225" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -10481,10 +10497,10 @@
         <v>515</v>
       </c>
       <c r="H226" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I226" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -10510,10 +10526,10 @@
         <v>515</v>
       </c>
       <c r="H227" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I227" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -10539,10 +10555,10 @@
         <v>515</v>
       </c>
       <c r="H228" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I228" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -10568,10 +10584,10 @@
         <v>515</v>
       </c>
       <c r="H229" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I229" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -10597,10 +10613,10 @@
         <v>515</v>
       </c>
       <c r="H230" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I230" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -10608,25 +10624,25 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C231" t="s">
+        <v>540</v>
+      </c>
+      <c r="D231" t="s">
         <v>539</v>
       </c>
-      <c r="D231" t="s">
-        <v>538</v>
-      </c>
       <c r="E231" t="s">
+        <v>540</v>
+      </c>
+      <c r="F231" t="s">
         <v>539</v>
       </c>
-      <c r="F231" t="s">
-        <v>538</v>
-      </c>
       <c r="G231" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H231" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I231" t="s">
         <v>185</v>
@@ -10637,28 +10653,28 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C232" t="s">
+        <v>540</v>
+      </c>
+      <c r="D232" t="s">
         <v>539</v>
       </c>
-      <c r="D232" t="s">
-        <v>538</v>
-      </c>
       <c r="E232" t="s">
+        <v>540</v>
+      </c>
+      <c r="F232" t="s">
         <v>539</v>
       </c>
-      <c r="F232" t="s">
-        <v>538</v>
-      </c>
       <c r="G232" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H232" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I232" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="233" spans="1:9">
@@ -10666,28 +10682,28 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C233" t="s">
+        <v>540</v>
+      </c>
+      <c r="D233" t="s">
         <v>539</v>
       </c>
-      <c r="D233" t="s">
-        <v>538</v>
-      </c>
       <c r="E233" t="s">
+        <v>540</v>
+      </c>
+      <c r="F233" t="s">
         <v>539</v>
       </c>
-      <c r="F233" t="s">
-        <v>538</v>
-      </c>
       <c r="G233" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H233" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I233" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -10695,28 +10711,28 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C234" t="s">
+        <v>540</v>
+      </c>
+      <c r="D234" t="s">
         <v>539</v>
       </c>
-      <c r="D234" t="s">
-        <v>538</v>
-      </c>
       <c r="E234" t="s">
+        <v>540</v>
+      </c>
+      <c r="F234" t="s">
         <v>539</v>
       </c>
-      <c r="F234" t="s">
-        <v>538</v>
-      </c>
       <c r="G234" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H234" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I234" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -10724,28 +10740,28 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C235" t="s">
+        <v>540</v>
+      </c>
+      <c r="D235" t="s">
         <v>539</v>
       </c>
-      <c r="D235" t="s">
-        <v>538</v>
-      </c>
       <c r="E235" t="s">
+        <v>540</v>
+      </c>
+      <c r="F235" t="s">
         <v>539</v>
       </c>
-      <c r="F235" t="s">
-        <v>538</v>
-      </c>
       <c r="G235" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H235" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I235" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -10753,28 +10769,28 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C236" t="s">
+        <v>540</v>
+      </c>
+      <c r="D236" t="s">
         <v>539</v>
       </c>
-      <c r="D236" t="s">
-        <v>538</v>
-      </c>
       <c r="E236" t="s">
+        <v>540</v>
+      </c>
+      <c r="F236" t="s">
         <v>539</v>
       </c>
-      <c r="F236" t="s">
-        <v>538</v>
-      </c>
       <c r="G236" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H236" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I236" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -10782,28 +10798,28 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C237" t="s">
+        <v>540</v>
+      </c>
+      <c r="D237" t="s">
         <v>539</v>
       </c>
-      <c r="D237" t="s">
-        <v>538</v>
-      </c>
       <c r="E237" t="s">
+        <v>540</v>
+      </c>
+      <c r="F237" t="s">
         <v>539</v>
       </c>
-      <c r="F237" t="s">
-        <v>538</v>
-      </c>
       <c r="G237" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H237" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I237" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="238" spans="1:9">
@@ -10811,28 +10827,28 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C238" t="s">
+        <v>540</v>
+      </c>
+      <c r="D238" t="s">
         <v>539</v>
       </c>
-      <c r="D238" t="s">
-        <v>538</v>
-      </c>
       <c r="E238" t="s">
+        <v>540</v>
+      </c>
+      <c r="F238" t="s">
         <v>539</v>
       </c>
-      <c r="F238" t="s">
-        <v>538</v>
-      </c>
       <c r="G238" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H238" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I238" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -10840,28 +10856,28 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C239" t="s">
+        <v>557</v>
+      </c>
+      <c r="D239" t="s">
         <v>556</v>
       </c>
-      <c r="D239" t="s">
-        <v>555</v>
-      </c>
       <c r="E239" t="s">
+        <v>557</v>
+      </c>
+      <c r="F239" t="s">
         <v>556</v>
       </c>
-      <c r="F239" t="s">
-        <v>555</v>
-      </c>
       <c r="G239" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H239" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I239" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -10869,28 +10885,28 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C240" t="s">
+        <v>557</v>
+      </c>
+      <c r="D240" t="s">
         <v>556</v>
       </c>
-      <c r="D240" t="s">
-        <v>555</v>
-      </c>
       <c r="E240" t="s">
+        <v>557</v>
+      </c>
+      <c r="F240" t="s">
         <v>556</v>
       </c>
-      <c r="F240" t="s">
-        <v>555</v>
-      </c>
       <c r="G240" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H240" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I240" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -10898,28 +10914,28 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C241" t="s">
+        <v>557</v>
+      </c>
+      <c r="D241" t="s">
         <v>556</v>
       </c>
-      <c r="D241" t="s">
-        <v>555</v>
-      </c>
       <c r="E241" t="s">
+        <v>557</v>
+      </c>
+      <c r="F241" t="s">
         <v>556</v>
       </c>
-      <c r="F241" t="s">
-        <v>555</v>
-      </c>
       <c r="G241" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H241" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I241" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -10927,28 +10943,28 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C242" t="s">
+        <v>557</v>
+      </c>
+      <c r="D242" t="s">
         <v>556</v>
       </c>
-      <c r="D242" t="s">
-        <v>555</v>
-      </c>
       <c r="E242" t="s">
+        <v>557</v>
+      </c>
+      <c r="F242" t="s">
         <v>556</v>
       </c>
-      <c r="F242" t="s">
-        <v>555</v>
-      </c>
       <c r="G242" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H242" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I242" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -10956,28 +10972,28 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C243" t="s">
+        <v>557</v>
+      </c>
+      <c r="D243" t="s">
         <v>556</v>
       </c>
-      <c r="D243" t="s">
-        <v>555</v>
-      </c>
       <c r="E243" t="s">
+        <v>557</v>
+      </c>
+      <c r="F243" t="s">
         <v>556</v>
       </c>
-      <c r="F243" t="s">
-        <v>555</v>
-      </c>
       <c r="G243" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H243" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I243" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -10985,28 +11001,28 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C244" t="s">
+        <v>557</v>
+      </c>
+      <c r="D244" t="s">
         <v>556</v>
       </c>
-      <c r="D244" t="s">
-        <v>555</v>
-      </c>
       <c r="E244" t="s">
+        <v>557</v>
+      </c>
+      <c r="F244" t="s">
         <v>556</v>
       </c>
-      <c r="F244" t="s">
-        <v>555</v>
-      </c>
       <c r="G244" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H244" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I244" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -11014,28 +11030,28 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C245" t="s">
+        <v>557</v>
+      </c>
+      <c r="D245" t="s">
         <v>556</v>
       </c>
-      <c r="D245" t="s">
-        <v>555</v>
-      </c>
       <c r="E245" t="s">
+        <v>557</v>
+      </c>
+      <c r="F245" t="s">
         <v>556</v>
       </c>
-      <c r="F245" t="s">
-        <v>555</v>
-      </c>
       <c r="G245" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H245" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I245" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -11043,28 +11059,28 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C246" t="s">
+        <v>557</v>
+      </c>
+      <c r="D246" t="s">
         <v>556</v>
       </c>
-      <c r="D246" t="s">
-        <v>555</v>
-      </c>
       <c r="E246" t="s">
+        <v>557</v>
+      </c>
+      <c r="F246" t="s">
         <v>556</v>
       </c>
-      <c r="F246" t="s">
-        <v>555</v>
-      </c>
       <c r="G246" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H246" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I246" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -11072,28 +11088,28 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C247" t="s">
+        <v>575</v>
+      </c>
+      <c r="D247" t="s">
         <v>574</v>
       </c>
-      <c r="D247" t="s">
-        <v>573</v>
-      </c>
       <c r="E247" t="s">
+        <v>575</v>
+      </c>
+      <c r="F247" t="s">
         <v>574</v>
       </c>
-      <c r="F247" t="s">
-        <v>573</v>
-      </c>
       <c r="G247" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H247" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I247" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -11101,28 +11117,28 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C248" t="s">
+        <v>575</v>
+      </c>
+      <c r="D248" t="s">
         <v>574</v>
       </c>
-      <c r="D248" t="s">
-        <v>573</v>
-      </c>
       <c r="E248" t="s">
+        <v>575</v>
+      </c>
+      <c r="F248" t="s">
         <v>574</v>
       </c>
-      <c r="F248" t="s">
-        <v>573</v>
-      </c>
       <c r="G248" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H248" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I248" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -11130,28 +11146,28 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C249" t="s">
+        <v>575</v>
+      </c>
+      <c r="D249" t="s">
         <v>574</v>
       </c>
-      <c r="D249" t="s">
-        <v>573</v>
-      </c>
       <c r="E249" t="s">
+        <v>575</v>
+      </c>
+      <c r="F249" t="s">
         <v>574</v>
       </c>
-      <c r="F249" t="s">
-        <v>573</v>
-      </c>
       <c r="G249" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H249" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I249" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="250" spans="1:9">
@@ -11159,28 +11175,28 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C250" t="s">
+        <v>575</v>
+      </c>
+      <c r="D250" t="s">
         <v>574</v>
       </c>
-      <c r="D250" t="s">
-        <v>573</v>
-      </c>
       <c r="E250" t="s">
+        <v>575</v>
+      </c>
+      <c r="F250" t="s">
         <v>574</v>
       </c>
-      <c r="F250" t="s">
-        <v>573</v>
-      </c>
       <c r="G250" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H250" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="I250" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -11188,28 +11204,28 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C251" t="s">
+        <v>575</v>
+      </c>
+      <c r="D251" t="s">
         <v>574</v>
       </c>
-      <c r="D251" t="s">
-        <v>573</v>
-      </c>
       <c r="E251" t="s">
+        <v>575</v>
+      </c>
+      <c r="F251" t="s">
         <v>574</v>
       </c>
-      <c r="F251" t="s">
-        <v>573</v>
-      </c>
       <c r="G251" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H251" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I251" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -11217,28 +11233,28 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C252" t="s">
+        <v>575</v>
+      </c>
+      <c r="D252" t="s">
         <v>574</v>
       </c>
-      <c r="D252" t="s">
-        <v>573</v>
-      </c>
       <c r="E252" t="s">
+        <v>575</v>
+      </c>
+      <c r="F252" t="s">
         <v>574</v>
       </c>
-      <c r="F252" t="s">
-        <v>573</v>
-      </c>
       <c r="G252" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H252" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I252" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -11246,28 +11262,28 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C253" t="s">
+        <v>575</v>
+      </c>
+      <c r="D253" t="s">
         <v>574</v>
       </c>
-      <c r="D253" t="s">
-        <v>573</v>
-      </c>
       <c r="E253" t="s">
+        <v>575</v>
+      </c>
+      <c r="F253" t="s">
         <v>574</v>
       </c>
-      <c r="F253" t="s">
-        <v>573</v>
-      </c>
       <c r="G253" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H253" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="I253" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -11275,28 +11291,28 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C254" t="s">
+        <v>575</v>
+      </c>
+      <c r="D254" t="s">
         <v>574</v>
       </c>
-      <c r="D254" t="s">
-        <v>573</v>
-      </c>
       <c r="E254" t="s">
+        <v>575</v>
+      </c>
+      <c r="F254" t="s">
         <v>574</v>
       </c>
-      <c r="F254" t="s">
-        <v>573</v>
-      </c>
       <c r="G254" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H254" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="I254" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -11304,28 +11320,28 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C255" t="s">
+        <v>575</v>
+      </c>
+      <c r="D255" t="s">
         <v>574</v>
       </c>
-      <c r="D255" t="s">
-        <v>573</v>
-      </c>
       <c r="E255" t="s">
+        <v>575</v>
+      </c>
+      <c r="F255" t="s">
         <v>574</v>
       </c>
-      <c r="F255" t="s">
-        <v>573</v>
-      </c>
       <c r="G255" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H255" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I255" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -11333,28 +11349,28 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C256" t="s">
+        <v>575</v>
+      </c>
+      <c r="D256" t="s">
         <v>574</v>
       </c>
-      <c r="D256" t="s">
-        <v>573</v>
-      </c>
       <c r="E256" t="s">
+        <v>575</v>
+      </c>
+      <c r="F256" t="s">
         <v>574</v>
       </c>
-      <c r="F256" t="s">
-        <v>573</v>
-      </c>
       <c r="G256" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H256" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I256" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -11362,28 +11378,28 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C257" t="s">
+        <v>575</v>
+      </c>
+      <c r="D257" t="s">
         <v>574</v>
       </c>
-      <c r="D257" t="s">
-        <v>573</v>
-      </c>
       <c r="E257" t="s">
+        <v>575</v>
+      </c>
+      <c r="F257" t="s">
         <v>574</v>
       </c>
-      <c r="F257" t="s">
-        <v>573</v>
-      </c>
       <c r="G257" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H257" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="I257" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -11391,28 +11407,28 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C258" t="s">
+        <v>575</v>
+      </c>
+      <c r="D258" t="s">
         <v>574</v>
       </c>
-      <c r="D258" t="s">
-        <v>573</v>
-      </c>
       <c r="E258" t="s">
+        <v>575</v>
+      </c>
+      <c r="F258" t="s">
         <v>574</v>
       </c>
-      <c r="F258" t="s">
-        <v>573</v>
-      </c>
       <c r="G258" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H258" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I258" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -11420,28 +11436,28 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C259" t="s">
+        <v>575</v>
+      </c>
+      <c r="D259" t="s">
         <v>574</v>
       </c>
-      <c r="D259" t="s">
-        <v>573</v>
-      </c>
       <c r="E259" t="s">
+        <v>575</v>
+      </c>
+      <c r="F259" t="s">
         <v>574</v>
       </c>
-      <c r="F259" t="s">
-        <v>573</v>
-      </c>
       <c r="G259" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H259" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I259" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -11449,28 +11465,28 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C260" t="s">
+        <v>575</v>
+      </c>
+      <c r="D260" t="s">
         <v>574</v>
       </c>
-      <c r="D260" t="s">
-        <v>573</v>
-      </c>
       <c r="E260" t="s">
+        <v>575</v>
+      </c>
+      <c r="F260" t="s">
         <v>574</v>
       </c>
-      <c r="F260" t="s">
-        <v>573</v>
-      </c>
       <c r="G260" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H260" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I260" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -11478,28 +11494,28 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C261" t="s">
+        <v>575</v>
+      </c>
+      <c r="D261" t="s">
         <v>574</v>
       </c>
-      <c r="D261" t="s">
-        <v>573</v>
-      </c>
       <c r="E261" t="s">
+        <v>575</v>
+      </c>
+      <c r="F261" t="s">
         <v>574</v>
       </c>
-      <c r="F261" t="s">
-        <v>573</v>
-      </c>
       <c r="G261" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H261" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I261" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -11507,28 +11523,28 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C262" t="s">
+        <v>575</v>
+      </c>
+      <c r="D262" t="s">
         <v>574</v>
       </c>
-      <c r="D262" t="s">
-        <v>573</v>
-      </c>
       <c r="E262" t="s">
+        <v>575</v>
+      </c>
+      <c r="F262" t="s">
         <v>574</v>
       </c>
-      <c r="F262" t="s">
-        <v>573</v>
-      </c>
       <c r="G262" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H262" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I262" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="263" spans="1:9">
@@ -11536,28 +11552,28 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C263" t="s">
+        <v>575</v>
+      </c>
+      <c r="D263" t="s">
         <v>574</v>
       </c>
-      <c r="D263" t="s">
-        <v>573</v>
-      </c>
       <c r="E263" t="s">
+        <v>575</v>
+      </c>
+      <c r="F263" t="s">
         <v>574</v>
       </c>
-      <c r="F263" t="s">
-        <v>573</v>
-      </c>
       <c r="G263" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H263" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I263" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="264" spans="1:9">
@@ -11565,28 +11581,28 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C264" t="s">
+        <v>575</v>
+      </c>
+      <c r="D264" t="s">
         <v>574</v>
       </c>
-      <c r="D264" t="s">
-        <v>573</v>
-      </c>
       <c r="E264" t="s">
+        <v>575</v>
+      </c>
+      <c r="F264" t="s">
         <v>574</v>
       </c>
-      <c r="F264" t="s">
-        <v>573</v>
-      </c>
       <c r="G264" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H264" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I264" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="265" spans="1:9">
@@ -11594,28 +11610,28 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C265" t="s">
+        <v>557</v>
+      </c>
+      <c r="D265" t="s">
         <v>556</v>
       </c>
-      <c r="D265" t="s">
-        <v>555</v>
-      </c>
       <c r="E265" t="s">
+        <v>557</v>
+      </c>
+      <c r="F265" t="s">
         <v>556</v>
       </c>
-      <c r="F265" t="s">
-        <v>555</v>
-      </c>
       <c r="G265" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H265" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I265" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -11623,28 +11639,28 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C266" t="s">
+        <v>557</v>
+      </c>
+      <c r="D266" t="s">
         <v>556</v>
       </c>
-      <c r="D266" t="s">
-        <v>555</v>
-      </c>
       <c r="E266" t="s">
+        <v>557</v>
+      </c>
+      <c r="F266" t="s">
         <v>556</v>
       </c>
-      <c r="F266" t="s">
-        <v>555</v>
-      </c>
       <c r="G266" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H266" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I266" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="267" spans="1:9">
@@ -11652,28 +11668,28 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C267" t="s">
+        <v>557</v>
+      </c>
+      <c r="D267" t="s">
         <v>556</v>
       </c>
-      <c r="D267" t="s">
-        <v>555</v>
-      </c>
       <c r="E267" t="s">
+        <v>557</v>
+      </c>
+      <c r="F267" t="s">
         <v>556</v>
       </c>
-      <c r="F267" t="s">
-        <v>555</v>
-      </c>
       <c r="G267" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H267" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I267" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="268" spans="1:9">
@@ -11681,28 +11697,28 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C268" t="s">
+        <v>557</v>
+      </c>
+      <c r="D268" t="s">
         <v>556</v>
       </c>
-      <c r="D268" t="s">
-        <v>555</v>
-      </c>
       <c r="E268" t="s">
+        <v>557</v>
+      </c>
+      <c r="F268" t="s">
         <v>556</v>
       </c>
-      <c r="F268" t="s">
-        <v>555</v>
-      </c>
       <c r="G268" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H268" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I268" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="269" spans="1:9">
@@ -11728,10 +11744,10 @@
         <v>159</v>
       </c>
       <c r="H269" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I269" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -11745,22 +11761,22 @@
         <v>181</v>
       </c>
       <c r="D270" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E270" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F270" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H270" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I270" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -11774,10 +11790,10 @@
         <v>181</v>
       </c>
       <c r="D271" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E271" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F271" t="s">
         <v>62</v>
@@ -11786,10 +11802,10 @@
         <v>63</v>
       </c>
       <c r="H271" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I271" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="272" spans="1:9">
@@ -11815,10 +11831,10 @@
         <v>63</v>
       </c>
       <c r="H272" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="I272" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="273" spans="1:9">
@@ -11826,28 +11842,28 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C273" t="s">
+        <v>575</v>
+      </c>
+      <c r="D273" t="s">
         <v>574</v>
       </c>
-      <c r="D273" t="s">
-        <v>573</v>
-      </c>
       <c r="E273" t="s">
+        <v>575</v>
+      </c>
+      <c r="F273" t="s">
         <v>574</v>
       </c>
-      <c r="F273" t="s">
-        <v>573</v>
-      </c>
       <c r="G273" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H273" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I273" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="274" spans="1:9">
@@ -11855,28 +11871,28 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C274" t="s">
+        <v>575</v>
+      </c>
+      <c r="D274" t="s">
         <v>574</v>
       </c>
-      <c r="D274" t="s">
-        <v>573</v>
-      </c>
       <c r="E274" t="s">
+        <v>575</v>
+      </c>
+      <c r="F274" t="s">
         <v>574</v>
       </c>
-      <c r="F274" t="s">
-        <v>573</v>
-      </c>
       <c r="G274" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H274" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I274" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="275" spans="1:9">
@@ -11884,28 +11900,28 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C275" t="s">
+        <v>575</v>
+      </c>
+      <c r="D275" t="s">
         <v>574</v>
       </c>
-      <c r="D275" t="s">
-        <v>573</v>
-      </c>
       <c r="E275" t="s">
+        <v>575</v>
+      </c>
+      <c r="F275" t="s">
         <v>574</v>
       </c>
-      <c r="F275" t="s">
-        <v>573</v>
-      </c>
       <c r="G275" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H275" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I275" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="276" spans="1:9">
@@ -11913,28 +11929,28 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C276" t="s">
+        <v>575</v>
+      </c>
+      <c r="D276" t="s">
         <v>574</v>
       </c>
-      <c r="D276" t="s">
-        <v>573</v>
-      </c>
       <c r="E276" t="s">
+        <v>575</v>
+      </c>
+      <c r="F276" t="s">
         <v>574</v>
       </c>
-      <c r="F276" t="s">
-        <v>573</v>
-      </c>
       <c r="G276" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H276" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I276" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -11960,10 +11976,10 @@
         <v>63</v>
       </c>
       <c r="H277" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I277" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="278" spans="1:9">
@@ -11971,28 +11987,28 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C278" t="s">
+        <v>575</v>
+      </c>
+      <c r="D278" t="s">
         <v>574</v>
       </c>
-      <c r="D278" t="s">
-        <v>573</v>
-      </c>
       <c r="E278" t="s">
+        <v>575</v>
+      </c>
+      <c r="F278" t="s">
         <v>574</v>
       </c>
-      <c r="F278" t="s">
-        <v>573</v>
-      </c>
       <c r="G278" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H278" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I278" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="279" spans="1:9">
@@ -12000,28 +12016,28 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C279" t="s">
+        <v>575</v>
+      </c>
+      <c r="D279" t="s">
         <v>574</v>
       </c>
-      <c r="D279" t="s">
-        <v>573</v>
-      </c>
       <c r="E279" t="s">
+        <v>575</v>
+      </c>
+      <c r="F279" t="s">
         <v>574</v>
       </c>
-      <c r="F279" t="s">
-        <v>573</v>
-      </c>
       <c r="G279" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H279" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="I279" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -12029,28 +12045,28 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C280" t="s">
+        <v>575</v>
+      </c>
+      <c r="D280" t="s">
         <v>574</v>
       </c>
-      <c r="D280" t="s">
-        <v>573</v>
-      </c>
       <c r="E280" t="s">
+        <v>575</v>
+      </c>
+      <c r="F280" t="s">
         <v>574</v>
       </c>
-      <c r="F280" t="s">
-        <v>573</v>
-      </c>
       <c r="G280" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H280" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I280" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="281" spans="1:9">
@@ -12058,28 +12074,28 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C281" t="s">
+        <v>575</v>
+      </c>
+      <c r="D281" t="s">
         <v>574</v>
       </c>
-      <c r="D281" t="s">
-        <v>573</v>
-      </c>
       <c r="E281" t="s">
+        <v>575</v>
+      </c>
+      <c r="F281" t="s">
         <v>574</v>
       </c>
-      <c r="F281" t="s">
-        <v>573</v>
-      </c>
       <c r="G281" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H281" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I281" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="282" spans="1:9">
@@ -12105,10 +12121,10 @@
         <v>14</v>
       </c>
       <c r="H282" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I282" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="283" spans="1:9">
@@ -12116,28 +12132,28 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C283" t="s">
+        <v>540</v>
+      </c>
+      <c r="D283" t="s">
         <v>539</v>
       </c>
-      <c r="D283" t="s">
-        <v>538</v>
-      </c>
       <c r="E283" t="s">
+        <v>540</v>
+      </c>
+      <c r="F283" t="s">
         <v>539</v>
       </c>
-      <c r="F283" t="s">
-        <v>538</v>
-      </c>
       <c r="G283" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H283" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="I283" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="284" spans="1:9">
@@ -12163,10 +12179,10 @@
         <v>63</v>
       </c>
       <c r="H284" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I284" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="285" spans="1:9">
@@ -12174,28 +12190,28 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C285" t="s">
+        <v>557</v>
+      </c>
+      <c r="D285" t="s">
         <v>556</v>
       </c>
-      <c r="D285" t="s">
-        <v>555</v>
-      </c>
       <c r="E285" t="s">
+        <v>557</v>
+      </c>
+      <c r="F285" t="s">
         <v>556</v>
       </c>
-      <c r="F285" t="s">
-        <v>555</v>
-      </c>
       <c r="G285" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H285" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I285" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="286" spans="1:9">
@@ -12203,28 +12219,28 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C286" t="s">
+        <v>659</v>
+      </c>
+      <c r="D286" t="s">
         <v>658</v>
       </c>
-      <c r="D286" t="s">
-        <v>657</v>
-      </c>
       <c r="E286" t="s">
+        <v>659</v>
+      </c>
+      <c r="F286" t="s">
         <v>658</v>
       </c>
-      <c r="F286" t="s">
-        <v>657</v>
-      </c>
       <c r="G286" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H286" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I286" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="287" spans="1:9">
@@ -12232,28 +12248,28 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C287" t="s">
+        <v>659</v>
+      </c>
+      <c r="D287" t="s">
         <v>658</v>
       </c>
-      <c r="D287" t="s">
-        <v>657</v>
-      </c>
       <c r="E287" t="s">
+        <v>659</v>
+      </c>
+      <c r="F287" t="s">
         <v>658</v>
       </c>
-      <c r="F287" t="s">
-        <v>657</v>
-      </c>
       <c r="G287" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H287" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I287" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="288" spans="1:9">
@@ -12261,28 +12277,28 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C288" t="s">
+        <v>665</v>
+      </c>
+      <c r="D288" t="s">
         <v>664</v>
       </c>
-      <c r="D288" t="s">
-        <v>663</v>
-      </c>
       <c r="E288" t="s">
+        <v>665</v>
+      </c>
+      <c r="F288" t="s">
         <v>664</v>
       </c>
-      <c r="F288" t="s">
-        <v>663</v>
-      </c>
       <c r="G288" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H288" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I288" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="289" spans="1:9">
@@ -12290,28 +12306,28 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C289" t="s">
+        <v>665</v>
+      </c>
+      <c r="D289" t="s">
         <v>664</v>
       </c>
-      <c r="D289" t="s">
-        <v>663</v>
-      </c>
       <c r="E289" t="s">
+        <v>665</v>
+      </c>
+      <c r="F289" t="s">
         <v>664</v>
       </c>
-      <c r="F289" t="s">
-        <v>663</v>
-      </c>
       <c r="G289" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H289" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I289" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -12319,28 +12335,28 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C290" t="s">
+        <v>665</v>
+      </c>
+      <c r="D290" t="s">
         <v>664</v>
       </c>
-      <c r="D290" t="s">
-        <v>663</v>
-      </c>
       <c r="E290" t="s">
+        <v>665</v>
+      </c>
+      <c r="F290" t="s">
         <v>664</v>
       </c>
-      <c r="F290" t="s">
-        <v>663</v>
-      </c>
       <c r="G290" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H290" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I290" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="291" spans="1:9">
@@ -12348,28 +12364,28 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C291" t="s">
+        <v>665</v>
+      </c>
+      <c r="D291" t="s">
         <v>664</v>
       </c>
-      <c r="D291" t="s">
-        <v>663</v>
-      </c>
       <c r="E291" t="s">
+        <v>665</v>
+      </c>
+      <c r="F291" t="s">
         <v>664</v>
       </c>
-      <c r="F291" t="s">
-        <v>663</v>
-      </c>
       <c r="G291" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H291" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="I291" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="292" spans="1:9">
@@ -12377,28 +12393,28 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C292" t="s">
+        <v>665</v>
+      </c>
+      <c r="D292" t="s">
         <v>664</v>
       </c>
-      <c r="D292" t="s">
-        <v>663</v>
-      </c>
       <c r="E292" t="s">
+        <v>665</v>
+      </c>
+      <c r="F292" t="s">
         <v>664</v>
       </c>
-      <c r="F292" t="s">
-        <v>663</v>
-      </c>
       <c r="G292" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H292" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="I292" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="293" spans="1:9">
@@ -12406,28 +12422,28 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C293" t="s">
+        <v>665</v>
+      </c>
+      <c r="D293" t="s">
         <v>664</v>
       </c>
-      <c r="D293" t="s">
-        <v>663</v>
-      </c>
       <c r="E293" t="s">
+        <v>665</v>
+      </c>
+      <c r="F293" t="s">
         <v>664</v>
       </c>
-      <c r="F293" t="s">
-        <v>663</v>
-      </c>
       <c r="G293" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H293" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="I293" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="294" spans="1:9">
@@ -12435,28 +12451,28 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C294" t="s">
+        <v>665</v>
+      </c>
+      <c r="D294" t="s">
         <v>664</v>
       </c>
-      <c r="D294" t="s">
-        <v>663</v>
-      </c>
       <c r="E294" t="s">
+        <v>665</v>
+      </c>
+      <c r="F294" t="s">
         <v>664</v>
       </c>
-      <c r="F294" t="s">
-        <v>663</v>
-      </c>
       <c r="G294" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H294" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I294" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="295" spans="1:9">
@@ -12464,28 +12480,28 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C295" t="s">
+        <v>665</v>
+      </c>
+      <c r="D295" t="s">
         <v>664</v>
       </c>
-      <c r="D295" t="s">
-        <v>663</v>
-      </c>
       <c r="E295" t="s">
+        <v>665</v>
+      </c>
+      <c r="F295" t="s">
         <v>664</v>
       </c>
-      <c r="F295" t="s">
-        <v>663</v>
-      </c>
       <c r="G295" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H295" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I295" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="296" spans="1:9">
@@ -12511,10 +12527,10 @@
         <v>63</v>
       </c>
       <c r="H296" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="I296" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="297" spans="1:9">
@@ -12540,10 +12556,10 @@
         <v>63</v>
       </c>
       <c r="H297" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I297" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="298" spans="1:9">
@@ -12569,10 +12585,10 @@
         <v>139</v>
       </c>
       <c r="H298" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="I298" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -12598,10 +12614,10 @@
         <v>159</v>
       </c>
       <c r="H299" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I299" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -12627,10 +12643,10 @@
         <v>159</v>
       </c>
       <c r="H300" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="I300" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="301" spans="1:9">
@@ -12656,10 +12672,10 @@
         <v>189</v>
       </c>
       <c r="H301" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="I301" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="302" spans="1:9">
@@ -12685,10 +12701,10 @@
         <v>189</v>
       </c>
       <c r="H302" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="I302" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="303" spans="1:9">
@@ -12714,10 +12730,10 @@
         <v>235</v>
       </c>
       <c r="H303" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I303" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="304" spans="1:9">
@@ -12743,10 +12759,10 @@
         <v>235</v>
       </c>
       <c r="H304" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="I304" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -12772,10 +12788,10 @@
         <v>189</v>
       </c>
       <c r="H305" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I305" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="306" spans="1:9">
@@ -12795,16 +12811,16 @@
         <v>187</v>
       </c>
       <c r="F306" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>201</v>
       </c>
       <c r="H306" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I306" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -12824,16 +12840,16 @@
         <v>187</v>
       </c>
       <c r="F307" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>201</v>
       </c>
       <c r="H307" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I307" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="308" spans="1:9">
@@ -12859,10 +12875,10 @@
         <v>63</v>
       </c>
       <c r="H308" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I308" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="309" spans="1:9">
@@ -12888,10 +12904,10 @@
         <v>63</v>
       </c>
       <c r="H309" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I309" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="310" spans="1:9">
@@ -12917,10 +12933,10 @@
         <v>63</v>
       </c>
       <c r="H310" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I310" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="311" spans="1:9">
@@ -12946,10 +12962,10 @@
         <v>242</v>
       </c>
       <c r="H311" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I311" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="312" spans="1:9">
@@ -12957,28 +12973,28 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C312" t="s">
+        <v>540</v>
+      </c>
+      <c r="D312" t="s">
         <v>539</v>
       </c>
-      <c r="D312" t="s">
-        <v>538</v>
-      </c>
       <c r="E312" t="s">
+        <v>540</v>
+      </c>
+      <c r="F312" t="s">
         <v>539</v>
       </c>
-      <c r="F312" t="s">
-        <v>538</v>
-      </c>
       <c r="G312" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H312" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="I312" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="313" spans="1:9">
@@ -12986,28 +13002,28 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C313" t="s">
+        <v>540</v>
+      </c>
+      <c r="D313" t="s">
         <v>539</v>
       </c>
-      <c r="D313" t="s">
-        <v>538</v>
-      </c>
       <c r="E313" t="s">
+        <v>540</v>
+      </c>
+      <c r="F313" t="s">
         <v>539</v>
       </c>
-      <c r="F313" t="s">
-        <v>538</v>
-      </c>
       <c r="G313" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H313" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I313" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="314" spans="1:9">
@@ -13033,10 +13049,10 @@
         <v>10</v>
       </c>
       <c r="H314" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I314" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="315" spans="1:9">
@@ -13062,10 +13078,10 @@
         <v>10</v>
       </c>
       <c r="H315" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I315" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -13091,10 +13107,10 @@
         <v>10</v>
       </c>
       <c r="H316" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I316" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -13120,10 +13136,10 @@
         <v>63</v>
       </c>
       <c r="H317" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I317" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -13131,28 +13147,28 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C318" t="s">
+        <v>659</v>
+      </c>
+      <c r="D318" t="s">
         <v>658</v>
       </c>
-      <c r="D318" t="s">
-        <v>657</v>
-      </c>
       <c r="E318" t="s">
+        <v>659</v>
+      </c>
+      <c r="F318" t="s">
         <v>658</v>
       </c>
-      <c r="F318" t="s">
-        <v>657</v>
-      </c>
       <c r="G318" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H318" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I318" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="319" spans="1:9">
@@ -13160,28 +13176,28 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C319" t="s">
+        <v>659</v>
+      </c>
+      <c r="D319" t="s">
         <v>658</v>
       </c>
-      <c r="D319" t="s">
-        <v>657</v>
-      </c>
       <c r="E319" t="s">
+        <v>659</v>
+      </c>
+      <c r="F319" t="s">
         <v>658</v>
       </c>
-      <c r="F319" t="s">
-        <v>657</v>
-      </c>
       <c r="G319" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H319" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I319" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -13207,10 +13223,10 @@
         <v>63</v>
       </c>
       <c r="H320" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="I320" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -13218,28 +13234,28 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C321" t="s">
+        <v>557</v>
+      </c>
+      <c r="D321" t="s">
         <v>556</v>
       </c>
-      <c r="D321" t="s">
-        <v>555</v>
-      </c>
       <c r="E321" t="s">
+        <v>557</v>
+      </c>
+      <c r="F321" t="s">
         <v>556</v>
       </c>
-      <c r="F321" t="s">
-        <v>555</v>
-      </c>
       <c r="G321" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H321" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="I321" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -13265,10 +13281,10 @@
         <v>14</v>
       </c>
       <c r="H322" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I322" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -13294,10 +13310,10 @@
         <v>14</v>
       </c>
       <c r="H323" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="I323" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -13323,10 +13339,10 @@
         <v>159</v>
       </c>
       <c r="H324" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="I324" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -13352,10 +13368,10 @@
         <v>34</v>
       </c>
       <c r="H325" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I325" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -13381,10 +13397,10 @@
         <v>34</v>
       </c>
       <c r="H326" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="I326" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="327" spans="1:9">
@@ -13410,10 +13426,10 @@
         <v>34</v>
       </c>
       <c r="H327" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I327" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="328" spans="1:9">
@@ -13439,10 +13455,10 @@
         <v>34</v>
       </c>
       <c r="H328" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="I328" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="329" spans="1:9">
@@ -13468,10 +13484,10 @@
         <v>34</v>
       </c>
       <c r="H329" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="I329" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="330" spans="1:9">
@@ -13497,10 +13513,10 @@
         <v>34</v>
       </c>
       <c r="H330" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="I330" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="331" spans="1:9">
@@ -13526,10 +13542,10 @@
         <v>34</v>
       </c>
       <c r="H331" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I331" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="332" spans="1:9">
@@ -13555,10 +13571,10 @@
         <v>34</v>
       </c>
       <c r="H332" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I332" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="333" spans="1:9">
@@ -13584,10 +13600,10 @@
         <v>34</v>
       </c>
       <c r="H333" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I333" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="334" spans="1:9">
@@ -13613,10 +13629,10 @@
         <v>67</v>
       </c>
       <c r="H334" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="I334" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="335" spans="1:9">
@@ -13638,14 +13654,14 @@
       <c r="F335" t="s">
         <v>108</v>
       </c>
-      <c r="G335" s="6" t="s">
+      <c r="G335" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H335" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I335" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="336" spans="1:9">
@@ -13667,14 +13683,14 @@
       <c r="F336" t="s">
         <v>108</v>
       </c>
-      <c r="G336" s="6" t="s">
+      <c r="G336" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H336" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="I336" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="337" spans="1:9">
@@ -13696,14 +13712,14 @@
       <c r="F337" t="s">
         <v>108</v>
       </c>
-      <c r="G337" s="6" t="s">
+      <c r="G337" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H337" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="I337" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="338" spans="1:9">
@@ -13725,14 +13741,14 @@
       <c r="F338" t="s">
         <v>108</v>
       </c>
-      <c r="G338" s="6" t="s">
+      <c r="G338" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H338" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="I338" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="339" spans="1:9">
@@ -13754,14 +13770,14 @@
       <c r="F339" t="s">
         <v>108</v>
       </c>
-      <c r="G339" s="6" t="s">
+      <c r="G339" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H339" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I339" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="340" spans="1:9">
@@ -13783,14 +13799,14 @@
       <c r="F340" t="s">
         <v>108</v>
       </c>
-      <c r="G340" s="6" t="s">
+      <c r="G340" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H340" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I340" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="341" spans="1:9">
@@ -13812,14 +13828,14 @@
       <c r="F341" t="s">
         <v>108</v>
       </c>
-      <c r="G341" s="6" t="s">
+      <c r="G341" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H341" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I341" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="342" spans="1:9">
@@ -13841,14 +13857,14 @@
       <c r="F342" t="s">
         <v>138</v>
       </c>
-      <c r="G342" s="6" t="s">
+      <c r="G342" s="7" t="s">
         <v>139</v>
       </c>
       <c r="H342" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I342" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -13870,14 +13886,14 @@
       <c r="F343" t="s">
         <v>108</v>
       </c>
-      <c r="G343" s="6" t="s">
+      <c r="G343" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H343" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I343" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -13899,14 +13915,14 @@
       <c r="F344" t="s">
         <v>108</v>
       </c>
-      <c r="G344" s="6" t="s">
+      <c r="G344" s="7" t="s">
         <v>109</v>
       </c>
       <c r="H344" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="I344" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -13932,10 +13948,10 @@
         <v>109</v>
       </c>
       <c r="H345" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="I345" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="346" spans="1:9">
@@ -13961,10 +13977,10 @@
         <v>139</v>
       </c>
       <c r="H346" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I346" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="347" spans="1:9">
@@ -13990,10 +14006,10 @@
         <v>47</v>
       </c>
       <c r="H347" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="I347" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="348" spans="1:9">
@@ -14019,10 +14035,10 @@
         <v>139</v>
       </c>
       <c r="H348" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="I348" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="349" spans="1:9">
@@ -14048,10 +14064,10 @@
         <v>139</v>
       </c>
       <c r="H349" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="I349" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="350" spans="1:9">
@@ -14077,10 +14093,10 @@
         <v>139</v>
       </c>
       <c r="H350" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="I350" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="351" spans="1:9">
@@ -14106,10 +14122,10 @@
         <v>159</v>
       </c>
       <c r="H351" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="I351" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="352" spans="1:9">
@@ -14135,10 +14151,10 @@
         <v>159</v>
       </c>
       <c r="H352" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="I352" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="353" spans="1:9">
@@ -14164,10 +14180,10 @@
         <v>67</v>
       </c>
       <c r="H353" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="I353" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="354" spans="1:9">
@@ -14193,10 +14209,10 @@
         <v>67</v>
       </c>
       <c r="H354" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I354" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="355" spans="1:9">
@@ -14222,10 +14238,10 @@
         <v>67</v>
       </c>
       <c r="H355" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="I355" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="356" spans="1:9">
@@ -14251,10 +14267,10 @@
         <v>67</v>
       </c>
       <c r="H356" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="I356" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="357" spans="1:9">
@@ -14280,10 +14296,10 @@
         <v>109</v>
       </c>
       <c r="H357" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="I357" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="358" spans="1:9">
@@ -14309,10 +14325,10 @@
         <v>34</v>
       </c>
       <c r="H358" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="I358" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="359" spans="1:9">
@@ -14338,10 +14354,10 @@
         <v>32</v>
       </c>
       <c r="H359" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="I359" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="360" spans="1:9">
@@ -14367,10 +14383,10 @@
         <v>34</v>
       </c>
       <c r="H360" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I360" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="361" spans="1:9">
@@ -14396,10 +14412,10 @@
         <v>67</v>
       </c>
       <c r="H361" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I361" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="362" spans="1:9">
@@ -14425,10 +14441,10 @@
         <v>139</v>
       </c>
       <c r="H362" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="I362" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="363" spans="1:9">
@@ -14448,10 +14464,10 @@
         <v>181</v>
       </c>
       <c r="H363" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="I363" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="364" spans="1:9">
@@ -14477,10 +14493,10 @@
         <v>63</v>
       </c>
       <c r="H364" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="I364" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="365" spans="1:9">
@@ -14506,10 +14522,10 @@
         <v>183</v>
       </c>
       <c r="H365" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I365" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="366" spans="1:9">
@@ -14523,22 +14539,22 @@
         <v>181</v>
       </c>
       <c r="D366" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E366" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F366" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G366" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H366" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I366" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="367" spans="1:9">
@@ -14552,22 +14568,22 @@
         <v>181</v>
       </c>
       <c r="D367" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E367" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F367" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H367" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="I367" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="368" spans="1:9">
@@ -14593,10 +14609,10 @@
         <v>183</v>
       </c>
       <c r="H368" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I368" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="369" spans="1:9">
@@ -14622,10 +14638,10 @@
         <v>183</v>
       </c>
       <c r="H369" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I369" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="370" spans="1:9">
@@ -14651,10 +14667,10 @@
         <v>183</v>
       </c>
       <c r="H370" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="I370" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="371" spans="1:9">
@@ -14680,10 +14696,10 @@
         <v>183</v>
       </c>
       <c r="H371" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="I371" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="372" spans="1:9">
@@ -14709,10 +14725,10 @@
         <v>189</v>
       </c>
       <c r="H372" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I372" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="373" spans="1:9">
@@ -14738,10 +14754,10 @@
         <v>189</v>
       </c>
       <c r="H373" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="I373" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="374" spans="1:9">
@@ -14767,10 +14783,10 @@
         <v>189</v>
       </c>
       <c r="H374" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I374" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="375" spans="1:9">
@@ -14796,10 +14812,10 @@
         <v>189</v>
       </c>
       <c r="H375" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="I375" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="376" spans="1:9">
@@ -14825,10 +14841,10 @@
         <v>189</v>
       </c>
       <c r="H376" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="I376" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="377" spans="1:9">
@@ -14854,10 +14870,10 @@
         <v>189</v>
       </c>
       <c r="H377" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="I377" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="378" spans="1:9">
@@ -14871,10 +14887,10 @@
         <v>181</v>
       </c>
       <c r="D378" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E378" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F378" t="s">
         <v>47</v>
@@ -14883,10 +14899,10 @@
         <v>47</v>
       </c>
       <c r="H378" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="I378" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="379" spans="1:9">
@@ -14912,10 +14928,10 @@
         <v>189</v>
       </c>
       <c r="H379" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="I379" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="380" spans="1:9">
@@ -14941,10 +14957,10 @@
         <v>189</v>
       </c>
       <c r="H380" t="s">
-        <v>851</v>
-      </c>
-      <c r="I380" s="7" t="s">
         <v>852</v>
+      </c>
+      <c r="I380" s="8" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="381" spans="1:9">
@@ -14970,10 +14986,10 @@
         <v>63</v>
       </c>
       <c r="H381" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I381" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="382" spans="1:9">
@@ -14999,10 +15015,10 @@
         <v>189</v>
       </c>
       <c r="H382" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I382" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="383" spans="1:9">
@@ -15028,10 +15044,10 @@
         <v>189</v>
       </c>
       <c r="H383" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="I383" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="384" spans="1:9">
@@ -15057,10 +15073,10 @@
         <v>47</v>
       </c>
       <c r="H384" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="I384" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="385" spans="1:9">
@@ -15086,10 +15102,10 @@
         <v>245</v>
       </c>
       <c r="H385" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I385" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="386" spans="1:9">
@@ -15115,10 +15131,10 @@
         <v>245</v>
       </c>
       <c r="H386" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="I386" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="387" spans="1:9">
@@ -15144,10 +15160,10 @@
         <v>245</v>
       </c>
       <c r="H387" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I387" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="388" spans="1:9">
@@ -15173,10 +15189,10 @@
         <v>245</v>
       </c>
       <c r="H388" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="I388" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="389" spans="1:9">
@@ -15202,10 +15218,10 @@
         <v>245</v>
       </c>
       <c r="H389" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="I389" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="390" spans="1:9">
@@ -15231,10 +15247,10 @@
         <v>245</v>
       </c>
       <c r="H390" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="I390" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="391" spans="1:9">
@@ -15260,10 +15276,10 @@
         <v>245</v>
       </c>
       <c r="H391" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="I391" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="392" spans="1:9">
@@ -15289,10 +15305,10 @@
         <v>245</v>
       </c>
       <c r="H392" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="I392" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="393" spans="1:9">
@@ -15318,10 +15334,10 @@
         <v>245</v>
       </c>
       <c r="H393" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="I393" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="394" spans="1:9">
@@ -15347,10 +15363,10 @@
         <v>245</v>
       </c>
       <c r="H394" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="I394" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="395" spans="1:9">
@@ -15376,10 +15392,10 @@
         <v>255</v>
       </c>
       <c r="H395" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="I395" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="396" spans="1:9">
@@ -15405,10 +15421,10 @@
         <v>255</v>
       </c>
       <c r="H396" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="I396" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="397" spans="1:9">
@@ -15434,10 +15450,10 @@
         <v>255</v>
       </c>
       <c r="H397" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="I397" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="398" spans="1:9">
@@ -15463,10 +15479,10 @@
         <v>255</v>
       </c>
       <c r="H398" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="I398" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="399" spans="1:9">
@@ -15492,10 +15508,10 @@
         <v>255</v>
       </c>
       <c r="H399" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="I399" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="400" spans="1:9">
@@ -15521,10 +15537,10 @@
         <v>245</v>
       </c>
       <c r="H400" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="I400" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="401" spans="1:9">
@@ -15550,10 +15566,10 @@
         <v>255</v>
       </c>
       <c r="H401" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="I401" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="402" spans="1:9">
@@ -15579,10 +15595,10 @@
         <v>47</v>
       </c>
       <c r="H402" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I402" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="403" spans="1:9">
@@ -15602,16 +15618,16 @@
         <v>331</v>
       </c>
       <c r="F403" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G403" t="s">
         <v>333</v>
       </c>
       <c r="H403" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="I403" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="404" spans="1:9">
@@ -15631,16 +15647,16 @@
         <v>331</v>
       </c>
       <c r="F404" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G404" t="s">
         <v>333</v>
       </c>
       <c r="H404" t="s">
-        <v>900</v>
-      </c>
-      <c r="I404" s="8" t="s">
         <v>901</v>
+      </c>
+      <c r="I404" s="9" t="s">
+        <v>902</v>
       </c>
     </row>
   </sheetData>
